--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.36617674112852</v>
+        <v>6.559503720433384</v>
       </c>
       <c r="D2" t="n">
-        <v>62.46707149805805</v>
+        <v>10.15089911843443</v>
       </c>
       <c r="E2" t="n">
-        <v>23.86233092167252</v>
+        <v>3.877628774771785</v>
       </c>
       <c r="F2" t="n">
-        <v>12.89967404760828</v>
+        <v>2.096197032736344</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>88.09083858447356</v>
+        <v>14.31476126997695</v>
       </c>
       <c r="D3" t="n">
-        <v>88.26641959327461</v>
+        <v>14.34329318390712</v>
       </c>
       <c r="E3" t="n">
-        <v>23.86233092167252</v>
+        <v>3.877628774771785</v>
       </c>
       <c r="F3" t="n">
-        <v>12.89967404760828</v>
+        <v>2.096197032736344</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
